--- a/public/file/mongcaipig-mau-import.xlsx
+++ b/public/file/mongcaipig-mau-import.xlsx
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="115">
   <si>
     <t/>
   </si>
@@ -340,21 +340,6 @@
     <t>pha_he</t>
   </si>
   <si>
-    <t>2021-10-05 15:09:00</t>
-  </si>
-  <si>
-    <t>2021-11-22 22:22:00</t>
-  </si>
-  <si>
-    <t>2021-11-26 22:22:00</t>
-  </si>
-  <si>
-    <t>2021-12-29 12:22:00</t>
-  </si>
-  <si>
-    <t>2021-12-30 22:22:00</t>
-  </si>
-  <si>
     <t>Mẹ</t>
   </si>
   <si>
@@ -389,6 +374,18 @@
   </si>
   <si>
     <t>2021-12-05</t>
+  </si>
+  <si>
+    <t>2021-11-22</t>
+  </si>
+  <si>
+    <t>2021-11-26</t>
+  </si>
+  <si>
+    <t>2021-12-30</t>
+  </si>
+  <si>
+    <t>2021-12-29</t>
   </si>
 </sst>
 </file>
@@ -396,7 +393,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="d\.m"/>
+    <numFmt numFmtId="164" formatCode="d\.m"/>
   </numFmts>
   <fonts count="9" x14ac:knownFonts="1">
     <font>
@@ -493,7 +490,7 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -909,7 +906,7 @@
     </row>
     <row r="2" spans="1:45" x14ac:dyDescent="0.2">
       <c r="A2" s="14" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="B2" s="5">
         <v>111</v>
@@ -921,7 +918,7 @@
         <v>1</v>
       </c>
       <c r="F2" s="14" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="G2" s="3" t="s">
         <v>2</v>
@@ -957,10 +954,10 @@
       </c>
       <c r="AH2" s="6"/>
       <c r="AM2" s="19" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="AN2" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="AO2" s="3" t="s">
         <v>10</v>
@@ -972,13 +969,13 @@
         <v>12</v>
       </c>
       <c r="AR2" s="16" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="AS2" s="6"/>
     </row>
     <row r="3" spans="1:45" x14ac:dyDescent="0.2">
       <c r="A3" s="14" t="s">
-        <v>100</v>
+        <v>111</v>
       </c>
       <c r="B3" s="5">
         <v>13001</v>
@@ -987,7 +984,7 @@
         <v>24</v>
       </c>
       <c r="F3" s="14" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>22</v>
@@ -1077,10 +1074,10 @@
         <v>5</v>
       </c>
       <c r="AM3" s="17" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="AN3" s="17" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="AO3" s="6" t="s">
         <v>10</v>
@@ -1092,12 +1089,12 @@
         <v>12</v>
       </c>
       <c r="AR3" s="16" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
     </row>
     <row r="4" spans="1:45" x14ac:dyDescent="0.2">
       <c r="A4" s="14" t="s">
-        <v>101</v>
+        <v>112</v>
       </c>
       <c r="B4" s="5">
         <v>13002</v>
@@ -1106,7 +1103,7 @@
         <v>24</v>
       </c>
       <c r="F4" s="14" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="G4" s="3" t="s">
         <v>22</v>
@@ -1202,10 +1199,10 @@
         <v>6</v>
       </c>
       <c r="AM4" s="18" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="AN4" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="AO4" s="6" t="s">
         <v>10</v>
@@ -1217,12 +1214,12 @@
         <v>12</v>
       </c>
       <c r="AR4" s="16" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
     </row>
     <row r="5" spans="1:45" x14ac:dyDescent="0.2">
       <c r="A5" s="14" t="s">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="B5" s="5">
         <v>13019</v>
@@ -1234,7 +1231,7 @@
         <v>24</v>
       </c>
       <c r="F5" s="14" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="G5" s="3" t="s">
         <v>36</v>
@@ -1333,10 +1330,10 @@
         <v>5</v>
       </c>
       <c r="AM5" s="17" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="AN5" s="17" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="AO5" s="6" t="s">
         <v>10</v>
@@ -1348,12 +1345,12 @@
         <v>12</v>
       </c>
       <c r="AR5" s="16" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
     </row>
     <row r="6" spans="1:45" x14ac:dyDescent="0.2">
       <c r="A6" s="14" t="s">
-        <v>103</v>
+        <v>113</v>
       </c>
       <c r="B6" s="5">
         <v>11020</v>
@@ -1365,7 +1362,7 @@
         <v>24</v>
       </c>
       <c r="F6" s="14" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="G6" s="3" t="s">
         <v>49</v>
@@ -1452,10 +1449,10 @@
         <v>19</v>
       </c>
       <c r="AM6" s="18" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="AN6" s="17" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="AO6" s="6" t="s">
         <v>10</v>
@@ -1467,7 +1464,7 @@
         <v>12</v>
       </c>
       <c r="AR6" s="16" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
     </row>
     <row r="7" spans="1:45" x14ac:dyDescent="0.2">

--- a/public/file/mongcaipig-mau-import.xlsx
+++ b/public/file/mongcaipig-mau-import.xlsx
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="119">
   <si>
     <t/>
   </si>
@@ -361,18 +361,6 @@
     <t>https://drive.google.com/uc?id=1tqA7iVMy0Vprq5OMet-TQaf0XrFU5Ipo</t>
   </si>
   <si>
-    <t>2021-10-05</t>
-  </si>
-  <si>
-    <t>2021-08-05</t>
-  </si>
-  <si>
-    <t>2021-11-05</t>
-  </si>
-  <si>
-    <t>2021-12-05</t>
-  </si>
-  <si>
     <t>2 tháng</t>
   </si>
   <si>
@@ -395,6 +383,21 @@
   </si>
   <si>
     <t>Cao Bá E</t>
+  </si>
+  <si>
+    <t>05-08-2021</t>
+  </si>
+  <si>
+    <t>21-12-2021</t>
+  </si>
+  <si>
+    <t>30-12-2021</t>
+  </si>
+  <si>
+    <t>24-09-2021</t>
+  </si>
+  <si>
+    <t>28-10-2021</t>
   </si>
 </sst>
 </file>
@@ -914,16 +917,16 @@
         <v>111</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="C2" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>1</v>
       </c>
       <c r="E2" s="14" t="s">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="F2" s="3" t="s">
         <v>2</v>
@@ -1027,16 +1030,16 @@
         <v>13001</v>
       </c>
       <c r="B3" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="C3" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>24</v>
       </c>
       <c r="E3" s="14" t="s">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="F3" s="3" t="s">
         <v>22</v>
@@ -1152,16 +1155,16 @@
         <v>13002</v>
       </c>
       <c r="B4" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="C4" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>24</v>
       </c>
       <c r="E4" s="14" t="s">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="F4" s="3" t="s">
         <v>22</v>
@@ -1286,13 +1289,13 @@
         <v>35</v>
       </c>
       <c r="C5" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>24</v>
       </c>
       <c r="E5" s="14" t="s">
-        <v>106</v>
+        <v>117</v>
       </c>
       <c r="F5" s="3" t="s">
         <v>36</v>
@@ -1417,13 +1420,13 @@
         <v>48</v>
       </c>
       <c r="C6" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="D6" s="3" t="s">
         <v>24</v>
       </c>
       <c r="E6" s="14" t="s">
-        <v>106</v>
+        <v>118</v>
       </c>
       <c r="F6" s="3" t="s">
         <v>49</v>
